--- a/public/import_template/v0.2node/node_init_data.xlsx
+++ b/public/import_template/v0.2node/node_init_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ddit\code\umi_max.260226_github\public\import_template\v0.2node\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D893B431-2DF1-4C00-956B-BAE26780E6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B500F4-E1DA-42E7-8FD3-15132FAF29CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="904" xr2:uid="{2868D11C-8FA6-4240-99BD-0AA8693D0C29}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="904" activeTab="4" xr2:uid="{2868D11C-8FA6-4240-99BD-0AA8693D0C29}"/>
   </bookViews>
   <sheets>
     <sheet name="sys_user" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2727" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="1020">
   <si>
     <t>user_id</t>
   </si>
@@ -3750,6 +3750,41 @@
   <si>
     <t>./example/ai/aitheme</t>
     <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计分析DC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BarChartOutlined</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>API 日志分析</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/easy_dev_dc/apiAnalysis</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>/easy_dev_dc/analysis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>./easy_dev_dc/analysis/ApiAnalysis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A1510</t>
+  </si>
+  <si>
+    <t>A1510</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -16873,7 +16908,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C59C8AD8-AAAA-4AFC-9FE9-78BB7A11FDFC}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="17.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="6" bestFit="1" customWidth="1"/>
@@ -17867,6 +17902,76 @@
       <c r="M27" s="10"/>
       <c r="N27" s="10">
         <v>2400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="12" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0</v>
+      </c>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8">
+        <v>1</v>
+      </c>
+      <c r="K28" s="8">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8">
+        <v>1</v>
+      </c>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="4">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="J29" s="4">
+        <v>1</v>
+      </c>
+      <c r="K29" s="10">
+        <v>0</v>
+      </c>
+      <c r="L29" s="10">
+        <v>1</v>
+      </c>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10">
+        <v>3010</v>
       </c>
     </row>
   </sheetData>
@@ -17993,7 +18098,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB69598-2052-4A85-93DC-70D83316375E}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.875" style="1" bestFit="1" customWidth="1"/>
@@ -18055,7 +18160,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A30" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A32" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -18655,14 +18760,14 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>195</v>
+        <v>1017</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D28" s="9">
         <v>45546</v>
@@ -18683,10 +18788,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>200</v>
+        <v>1018</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D29" s="9">
         <v>45546</v>
@@ -18707,7 +18812,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>239</v>
@@ -18722,6 +18827,54 @@
         <v>45546</v>
       </c>
       <c r="G30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="9">
+        <v>45546</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="9">
+        <v>45546</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D32" s="9">
+        <v>45546</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" s="9">
+        <v>45546</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/public/import_template/v0.2node/node_init_data.xlsx
+++ b/public/import_template/v0.2node/node_init_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ddit\code\umi_max.260226_github\public\import_template\v0.2node\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B500F4-E1DA-42E7-8FD3-15132FAF29CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A75357-065C-4BC7-A3D3-714E34638883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="904" activeTab="4" xr2:uid="{2868D11C-8FA6-4240-99BD-0AA8693D0C29}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="867" activeTab="2" xr2:uid="{2868D11C-8FA6-4240-99BD-0AA8693D0C29}"/>
   </bookViews>
   <sheets>
     <sheet name="sys_user" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2753" uniqueCount="1024">
   <si>
     <t>user_id</t>
   </si>
@@ -3784,6 +3784,22 @@
   </si>
   <si>
     <t>A1510</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A1520</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应用日志分析</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/easy_dev_dc/appAnalysis</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>./easy_dev_dc/analysis/AppAnalysis</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -16908,7 +16924,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C59C8AD8-AAAA-4AFC-9FE9-78BB7A11FDFC}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="17.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="6" bestFit="1" customWidth="1"/>
@@ -17970,8 +17986,44 @@
         <v>1</v>
       </c>
       <c r="M29" s="10"/>
-      <c r="N29" s="10">
-        <v>3010</v>
+      <c r="N29" s="4">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="4">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J30" s="4">
+        <v>1</v>
+      </c>
+      <c r="K30" s="10">
+        <v>0</v>
+      </c>
+      <c r="L30" s="10">
+        <v>1</v>
+      </c>
+      <c r="M30" s="10"/>
+      <c r="N30" s="4">
+        <v>1520</v>
       </c>
     </row>
   </sheetData>
@@ -18098,7 +18150,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB69598-2052-4A85-93DC-70D83316375E}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.875" style="1" bestFit="1" customWidth="1"/>
@@ -18160,7 +18212,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A32" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A33" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -18812,10 +18864,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>195</v>
+        <v>1020</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D30" s="9">
         <v>45546</v>
@@ -18836,7 +18888,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>239</v>
@@ -18860,7 +18912,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>239</v>
@@ -18875,6 +18927,30 @@
         <v>45546</v>
       </c>
       <c r="G32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D33" s="9">
+        <v>45546</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" s="9">
+        <v>45546</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/public/import_template/v0.2node/node_init_data.xlsx
+++ b/public/import_template/v0.2node/node_init_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ddit\code\umi_max.260226_github\public\import_template\v0.2node\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A75357-065C-4BC7-A3D3-714E34638883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A6C72D-31DA-45C5-A531-7499C69E420D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="867" activeTab="2" xr2:uid="{2868D11C-8FA6-4240-99BD-0AA8693D0C29}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="867" activeTab="2" xr2:uid="{2868D11C-8FA6-4240-99BD-0AA8693D0C29}"/>
   </bookViews>
   <sheets>
     <sheet name="sys_user" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="app_module_field" sheetId="9" r:id="rId12"/>
     <sheet name="sys_customer_codetable" sheetId="17" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2753" uniqueCount="1024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2762" uniqueCount="1028">
   <si>
     <t>user_id</t>
   </si>
@@ -3800,6 +3800,22 @@
   </si>
   <si>
     <t>./easy_dev_dc/analysis/AppAnalysis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A1120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI模块生成</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>./easy_dev_dc/ai/module_generator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/easy_dev_dc/module_generator</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -16924,7 +16940,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C59C8AD8-AAAA-4AFC-9FE9-78BB7A11FDFC}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultColWidth="17.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="6" bestFit="1" customWidth="1"/>
@@ -17419,87 +17435,87 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="10">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10" t="s">
+        <v>1026</v>
+      </c>
+      <c r="J14" s="10">
+        <v>1</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10">
+        <v>1</v>
+      </c>
+      <c r="M14" s="10"/>
+      <c r="N14" s="4">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8" t="s">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="12" t="s">
+      <c r="E15" s="8"/>
+      <c r="F15" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G15" s="8">
         <v>0</v>
       </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8">
-        <v>1</v>
-      </c>
-      <c r="K14" s="8">
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8">
+        <v>1</v>
+      </c>
+      <c r="K15" s="8">
         <v>0</v>
       </c>
-      <c r="L14" s="8">
-        <v>1</v>
-      </c>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8">
+      <c r="L15" s="8">
+        <v>1</v>
+      </c>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8">
         <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>778</v>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="J15" s="4">
-        <v>1</v>
-      </c>
-      <c r="K15" s="10">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10">
-        <v>1</v>
-      </c>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10">
-        <v>2010</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="50"/>
@@ -17508,7 +17524,7 @@
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J16" s="4">
         <v>1</v>
@@ -17521,21 +17537,21 @@
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
-        <v>2020</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="50"/>
@@ -17544,7 +17560,7 @@
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J17" s="4">
         <v>1</v>
@@ -17557,21 +17573,21 @@
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>562</v>
+        <v>223</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>780</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="50"/>
@@ -17579,8 +17595,8 @@
         <v>0</v>
       </c>
       <c r="H18" s="4"/>
-      <c r="I18" s="31" t="s">
-        <v>563</v>
+      <c r="I18" s="4" t="s">
+        <v>229</v>
       </c>
       <c r="J18" s="4">
         <v>1</v>
@@ -17593,21 +17609,21 @@
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
-        <v>2040</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="50"/>
@@ -17629,21 +17645,21 @@
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
-        <v>2050</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>613</v>
+        <v>236</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>615</v>
+      <c r="C20" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>620</v>
+        <v>561</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="50"/>
@@ -17665,21 +17681,21 @@
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
-        <v>2060</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="50"/>
@@ -17701,21 +17717,21 @@
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
-        <v>2070</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>666</v>
+        <v>614</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>667</v>
-      </c>
-      <c r="D22" s="45" t="s">
-        <v>668</v>
+        <v>616</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>618</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="50"/>
@@ -17724,7 +17740,7 @@
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="31" t="s">
-        <v>669</v>
+        <v>563</v>
       </c>
       <c r="J22" s="4">
         <v>1</v>
@@ -17737,30 +17753,30 @@
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>731</v>
+        <v>666</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>732</v>
+        <v>667</v>
       </c>
       <c r="D23" s="45" t="s">
-        <v>733</v>
+        <v>668</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="50"/>
       <c r="G23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="4"/>
-      <c r="I23" s="4" t="s">
-        <v>734</v>
+      <c r="I23" s="31" t="s">
+        <v>669</v>
       </c>
       <c r="J23" s="4">
         <v>1</v>
@@ -17773,30 +17789,30 @@
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>781</v>
+        <v>731</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>782</v>
+        <v>732</v>
       </c>
       <c r="D24" s="45" t="s">
-        <v>783</v>
+        <v>733</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="50"/>
       <c r="G24" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="4"/>
-      <c r="I24" s="31" t="s">
-        <v>784</v>
+      <c r="I24" s="4" t="s">
+        <v>734</v>
       </c>
       <c r="J24" s="4">
         <v>1</v>
@@ -17809,21 +17825,21 @@
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
-        <v>2100</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>889</v>
+        <v>781</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>1008</v>
+        <v>782</v>
       </c>
       <c r="D25" s="45" t="s">
-        <v>1009</v>
+        <v>783</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="50"/>
@@ -17832,7 +17848,7 @@
       </c>
       <c r="H25" s="4"/>
       <c r="I25" s="31" t="s">
-        <v>1010</v>
+        <v>784</v>
       </c>
       <c r="J25" s="4">
         <v>1</v>
@@ -17845,21 +17861,21 @@
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
-        <v>2200</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>967</v>
+        <v>889</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>951</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>966</v>
+        <v>1008</v>
+      </c>
+      <c r="D26" s="45" t="s">
+        <v>1009</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="50"/>
@@ -17868,7 +17884,7 @@
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="31" t="s">
-        <v>563</v>
+        <v>1010</v>
       </c>
       <c r="J26" s="4">
         <v>1</v>
@@ -17881,21 +17897,21 @@
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
-        <v>2300</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>1007</v>
+        <v>967</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="50"/>
@@ -17917,91 +17933,91 @@
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>958</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>968</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="4">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="31" t="s">
+        <v>563</v>
+      </c>
+      <c r="J28" s="4">
+        <v>1</v>
+      </c>
+      <c r="K28" s="10">
+        <v>0</v>
+      </c>
+      <c r="L28" s="10">
+        <v>1</v>
+      </c>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10">
         <v>2400</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="8" t="s">
         <v>1017</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8" t="s">
+      <c r="B29" s="8"/>
+      <c r="C29" s="8" t="s">
         <v>1011</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D29" s="8" t="s">
         <v>1015</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="12" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="12" t="s">
         <v>1012</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G29" s="8">
         <v>0</v>
       </c>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8">
-        <v>1</v>
-      </c>
-      <c r="K28" s="8">
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8">
+        <v>1</v>
+      </c>
+      <c r="K29" s="8">
         <v>0</v>
       </c>
-      <c r="L28" s="8">
-        <v>1</v>
-      </c>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8">
+      <c r="L29" s="8">
+        <v>1</v>
+      </c>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8">
         <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="4">
-        <v>0</v>
-      </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="J29" s="4">
-        <v>1</v>
-      </c>
-      <c r="K29" s="10">
-        <v>0</v>
-      </c>
-      <c r="L29" s="10">
-        <v>1</v>
-      </c>
-      <c r="M29" s="10"/>
-      <c r="N29" s="4">
-        <v>1510</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>1017</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="50"/>
@@ -18010,7 +18026,7 @@
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="J30" s="4">
         <v>1</v>
@@ -18023,6 +18039,42 @@
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="4">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="4">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J31" s="4">
+        <v>1</v>
+      </c>
+      <c r="K31" s="10">
+        <v>0</v>
+      </c>
+      <c r="L31" s="10">
+        <v>1</v>
+      </c>
+      <c r="M31" s="10"/>
+      <c r="N31" s="4">
         <v>1520</v>
       </c>
     </row>
@@ -18150,7 +18202,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB69598-2052-4A85-93DC-70D83316375E}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.875" style="1" bestFit="1" customWidth="1"/>
@@ -18212,7 +18264,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A33" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A34" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -18480,7 +18532,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>195</v>
+        <v>1024</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>238</v>
@@ -18504,7 +18556,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>238</v>
@@ -18528,7 +18580,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>238</v>
@@ -18552,7 +18604,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>238</v>
@@ -18576,7 +18628,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>238</v>
@@ -18600,7 +18652,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>238</v>
@@ -18624,7 +18676,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>613</v>
+        <v>236</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>238</v>
@@ -18648,7 +18700,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>238</v>
@@ -18672,7 +18724,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>666</v>
+        <v>614</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>238</v>
@@ -18696,7 +18748,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>731</v>
+        <v>666</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>238</v>
@@ -18720,7 +18772,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>781</v>
+        <v>731</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>238</v>
@@ -18744,7 +18796,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>889</v>
+        <v>781</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>238</v>
@@ -18768,7 +18820,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>967</v>
+        <v>889</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>238</v>
@@ -18792,7 +18844,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1007</v>
+        <v>967</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>238</v>
@@ -18812,11 +18864,11 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1017</v>
+        <v>1007</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>238</v>
@@ -18836,11 +18888,11 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>238</v>
@@ -18864,7 +18916,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>238</v>
@@ -18888,10 +18940,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>195</v>
+        <v>1020</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D31" s="9">
         <v>45546</v>
@@ -18912,7 +18964,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>239</v>
@@ -18936,7 +18988,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>239</v>
@@ -18951,6 +19003,30 @@
         <v>45546</v>
       </c>
       <c r="G33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D34" s="9">
+        <v>45546</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34" s="9">
+        <v>45546</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/public/import_template/v0.2node/node_init_data.xlsx
+++ b/public/import_template/v0.2node/node_init_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ddit\code\umi_max.260226_github\public\import_template\v0.2node\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A6C72D-31DA-45C5-A531-7499C69E420D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B19B854-73FB-4DF4-9F72-084B6B5CEBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="867" activeTab="2" xr2:uid="{2868D11C-8FA6-4240-99BD-0AA8693D0C29}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="867" activeTab="4" xr2:uid="{2868D11C-8FA6-4240-99BD-0AA8693D0C29}"/>
   </bookViews>
   <sheets>
     <sheet name="sys_user" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2762" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2782" uniqueCount="1030">
   <si>
     <t>user_id</t>
   </si>
@@ -3816,6 +3816,14 @@
   </si>
   <si>
     <t>/easy_dev_dc/module_generator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test_sc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test_wm</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4550,7 +4558,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{107EB995-4C89-4582-B76D-10F8FFEE9BF1}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.125" style="1" customWidth="1"/>
@@ -4698,6 +4706,72 @@
         <v>45538</v>
       </c>
       <c r="K4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D5" s="2">
+        <v>123456</v>
+      </c>
+      <c r="E5" s="2">
+        <v>13000000000</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="9">
+        <v>45546</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="9">
+        <v>45538</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D6" s="2">
+        <v>123456</v>
+      </c>
+      <c r="E6" s="2">
+        <v>13000000000</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="9">
+        <v>45546</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="9">
+        <v>45538</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -18088,7 +18162,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0335A94-0B86-44BA-A74E-4E3DEDEB0EBE}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
@@ -18190,6 +18264,52 @@
         <v>45546</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="9">
+        <v>45546</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="9">
+        <v>45546</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D6" s="9">
+        <v>45546</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="9">
+        <v>45546</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
